--- a/data/sxbet/ligas/Super League/trades.xlsx
+++ b/data/sxbet/ligas/Super League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,334 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0xd238f20fcde288ce4c57fbb8f7b33433a2d8034453a92004f2884ec326a64527</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.99999</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1785472452</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3.493432</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0x1e132fb445f06c70fb459988df209de859a4064a819ad6bab3740c5a3eb17da8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.99999</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785472090</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3.493432</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0x7417df48500a21fdf17e408e1817d476b873de30de27e939dc5f140ed6eb83a4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.5737</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Super League</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>FC Basel vs FC Lausanne-Sport</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>FC Lausanne-Sport</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19608292</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1785344488</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1785600000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1.742902</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Super League/trades.xlsx
+++ b/data/sxbet/ligas/Super League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd238f20fcde288ce4c57fbb8f7b33433a2d8034453a92004f2884ec326a64527</t>
+          <t>0x889e4c26c8a497a646ccffadb2f3f1b24dbae2ec22c086b0017396209f4af21f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.2475</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Basel vs FC Lausanne-Sport</t>
+          <t>FC Zurich vs Servette FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FC Lausanne-Sport</t>
+          <t>Servette FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+          <t>0x61244a60fe501c549ef4ca5282d1ed97698790b1d8459a85a4e6a752833db822</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19608292</t>
+          <t>L19612584</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785472452</t>
+          <t>1785498956</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.493432</t>
+          <t>179.070707</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x1e132fb445f06c70fb459988df209de859a4064a819ad6bab3740c5a3eb17da8</t>
+          <t>0x7e466b51d045dd066cda83c12f2c992ec4cbeefd40776cc17f43d42835cf1a8c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>86.17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.2425</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,24 +673,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Super League</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>FC Basel vs FC Lausanne-Sport</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>FC Basel</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>FC Lausanne-Sport</t>
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+          <t>0x6271898b21228abd7c9953532c10606a3a61b7474b6c0e00b81d6846b2a3a400</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785472090</t>
+          <t>1785498935</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.493432</t>
+          <t>355.340206</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,110 +755,334 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0xd238f20fcde288ce4c57fbb8f7b33433a2d8034453a92004f2884ec326a64527</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.99999</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785472452</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3.493432</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x1e132fb445f06c70fb459988df209de859a4064a819ad6bab3740c5a3eb17da8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.99999</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785472090</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3.493432</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>0x7417df48500a21fdf17e408e1817d476b873de30de27e939dc5f140ed6eb83a4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.5737</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Super League</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>FC Basel vs FC Lausanne-Sport</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>FC Lausanne-Sport</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>L19608292</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1785344488</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1785600000</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1.742902</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Super League/trades.xlsx
+++ b/data/sxbet/ligas/Super League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x889e4c26c8a497a646ccffadb2f3f1b24dbae2ec22c086b0017396209f4af21f</t>
+          <t>0xc4b78f81e74dea13d41627a1344b91f28428a4324238d6f0145dee1a35efb8c3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>112.09999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2475</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,11 +555,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Super League</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FC Zurich vs Servette FC</t>
+          <t>FC Basel vs FC Lausanne-Sport</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>FC Basel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Servette FC</t>
+          <t>FC Lausanne-Sport</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x61244a60fe501c549ef4ca5282d1ed97698790b1d8459a85a4e6a752833db822</t>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19612584</t>
+          <t>L19608292</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785498956</t>
+          <t>1785576688</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>179.070707</t>
+          <t>149.71618</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7e466b51d045dd066cda83c12f2c992ec4cbeefd40776cc17f43d42835cf1a8c</t>
+          <t>0xd7a2e2cd3194f070ec5a6c369fd812f5f92b48d9d9d6ac2db522f13b6ee9ebcd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>86.17</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2425</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FC Basel vs FC Lausanne-Sport</t>
+          <t>FC Thun vs BSC Young Boys</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>FC Basel</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>FC Lausanne-Sport</t>
+          <t>BSC Young Boys</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x6271898b21228abd7c9953532c10606a3a61b7474b6c0e00b81d6846b2a3a400</t>
+          <t>0xc23f97461705ae01eb5a58d27789cd3f435cbaff7dc2c6e0adb3728285adb92a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19608292</t>
+          <t>L19611697</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785498935</t>
+          <t>1785576582</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785600000</t>
+          <t>1785609000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>355.340206</t>
+          <t>48.779487</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,54 +747,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd238f20fcde288ce4c57fbb8f7b33433a2d8034453a92004f2884ec326a64527</t>
+          <t>0xe3d43c5304f371b3dc5c007e98897e0aa821ca9c6472f8a3bd29341f06a9051f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.3475</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+          <t>Asian Handicap (0)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Super League</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>FC Basel vs FC Lausanne-Sport</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>FC Basel</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>FC Lausanne-Sport</t>
@@ -810,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+          <t>0xac3d55012754045044a228fb2fe0b04b00e062de300fe737cddab8432861b89e</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785472452</t>
+          <t>1785575852</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.493432</t>
+          <t>2.877698</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,54 +851,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1e132fb445f06c70fb459988df209de859a4064a819ad6bab3740c5a3eb17da8</t>
+          <t>0x8ec90a063babc52514910fde2bc216acbe90a31c9e3e0fece55e3010a2569c20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.99999</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5725</t>
+          <t>1.3425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Super League</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>FC Basel vs FC Lausanne-Sport</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>FC Basel</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>FC Lausanne-Sport</t>
@@ -922,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+          <t>0x65512100a255c4b2132b662901cd2e8bf4c98dc4f098799ffb85c37b57886ed5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785472090</t>
+          <t>1785575823</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.493432</t>
+          <t>15.708029</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,110 +955,4814 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>0x25b0fa7edac87c88567b6ae18e92c5c5c430bea7cb85c1b67694245f854060ac</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>13.4221</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.3388</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x65512100a255c4b2132b662901cd2e8bf4c98dc4f098799ffb85c37b57886ed5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785575487</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>39.622435</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x6474158a9e63a89e0e3b0a80e33eb8d3409fb16336bcff960b78f46e07ffa84e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.7525</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785575432</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6.644492</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0xbd667d40c7cada4d6b75431c9056a08e10325bdc2f79eb77b81a3ee91f9d888d</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.99998</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.7525</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785575430</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6.644492</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x4788ee64d9503a2c8d506a1633ce4875562a0201a3d5cf0f0ac625fc5e954a6e</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.7525</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785575429</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6.591362</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xba2a9e8cc5b327e98a2cb7379ba136e2150b828b567da4251760ab24f4b07243</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785575420</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x77bf872f7181a0b072d287f8bbe3587f11b160b49ebee91189b9d74103431331</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>86.2435</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.7512</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785575420</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>114.8</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x4ea20469d35fdc566358b0d68a773d5501383e33ebc305dc69e745f53707ae27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>19.45999</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.7512</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785575420</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>25.903481</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x6e0192627e95bb693d45b060f4054b245ba269f1211cd78347d2d7bfe564f6ec</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785575217</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4.901503</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x3bd544177117ea767bfd150ccf86ac88a6af5b847bc3291290f2f6c8eaecfb90</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.95999</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785575215</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6.624361</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x0e14cea9ae97bb0a8761baa7ccfee5a9b26ac20ae74b7d92b9a0f5fe23614923</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21.87</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785575213</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>29.208681</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x2c78c144c6606ad312cf2ad03a6bf1ad4048210cfeb172cf60404469547c7126</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xB1f9FaAaA197461Cdd2588315437130d4A47B1F6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.2563</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785574747</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>11.434146</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x82e2800ad237183a74b6acf622be02523261da08753dfff47f7180c343a78901</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>38.45998</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785574123</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>51.365583</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0xacb2d9e8fd3c0daacc0f1a869c400ef8d3632a8af33837fcea162e1bdbd796c5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5.25918</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.1775</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xced81494acf00b3bb5c36e614ce2c91cc8ab87ed3eb84aeb5283a1571d7fb834</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785574021</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>29.629183</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0xeed6bcdb21e896f74409baac24916951cc82f7e7f01d5b0e60ecbb1b1b6be720</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>24.16998</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785573913</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>32.280441</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0xf70f75b8a510c1b7645da45ecd63dcbf3457095d21f3a69461abd80734233b2e</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>58.98255</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785573659</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>78.6434</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x12233c3aa8665e0fa9bb1981db06cd4178055a418f8ec60f6101b679e8bc5910</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.99998</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785573580</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.335533</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x27979bbc37057ec80f8898f1458207fd4ca5726c3911fbbe1a9a1f7f60c68d0a</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>11.80999</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785572017</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>15.772942</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xd4b89fbdcae8565bbb4cf888ea7100e3017cddf7ab9a386b35b4470b84a32266</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>63.57</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785571887</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>84.901503</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x95f5a766279401cfacb40124ec511a0f8936fb7e97033db90b90294cce313cc7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.9953</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.7488</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785571887</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.329282</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x177ae5a2b0574082f4cda4c580f8c702c37d35572198e338d05a5e2b04909027</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.165</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x5aece18b7dbd998ce1051a8ed1db85bde0e8e985a55fe9ba0dc930008f0ed780</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785571887</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>13.575758</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0xf85a14e80b3089082a17e9062f0fe07fb6dfd87c27daf52ddd39cdedb125fb4d</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.2075</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xc44a18fc82345a2e2680fab46da92a74968cd59b6ad6ba08348abe0c53e46890</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785571886</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>4.915663</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x32495a1b00633fe7865dc3db4a80dbeefea347173ae2c4fcdd458bd1bc4ea8e4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.7475</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785571886</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.337793</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xcb07e6c1d36180201095fa5a8745815afae3184089d983f888c2c303169ca5e6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>9.99998</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.7475</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x8b61832481ba3955ed773a28dee5545cc4e44bbb1500cd737966ed534a73ab97</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785571851</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13.3779</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0xc8d1627251957208a95501da18ad277cc8ecd2fad9efebfb9d045eb63583cda5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.5225</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>FC Zurich vs Servette FC</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>FC Zurich</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Servette FC</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xc8d13376550c3fb83d63242e1709127cf9b21c143a7300d232506ddbf987f819</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19612584</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785566165</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>8.593301</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xbacbcc8268a8097ae120992773ac001d4ce63fabe9170ab9b534d5960d0f24a9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>29.51</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x714b94ab9fe7c3181cb239c743b1739a5f8faf1aeba493c71aee3987557a383c</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785560273</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x9b09718c62cd0bbdead9998b19658325f57474b47d5790ec034d62856856d25e</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>17.32252</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x27f03841ab4a6d97175c7cc224e59b6651eb8c019d998731a01f130598ddf62d</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785560273</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>43.037317</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x0d84125ab8bbbbcd7f75d6f009b7c399296097be07ef4c8bb3d246bc9ede4e78</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.4025</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x27f03841ab4a6d97175c7cc224e59b6651eb8c019d998731a01f130598ddf62d</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785560273</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>72.049689</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0xde2fecb18b6a7ccffd2480bd930528ad33a82d82c426c88d4799e7127472cefb</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>13.67749</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.4025</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x27f03841ab4a6d97175c7cc224e59b6651eb8c019d998731a01f130598ddf62d</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785560272</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>33.981342</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x90050958de2d53fb884ae86545d2fc3fc5301fb83ff02fcdd65f5654974af210</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xc23f97461705ae01eb5a58d27789cd3f435cbaff7dc2c6e0adb3728285adb92a</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785560272</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x2fc619872088922c598f7c335a38829c307f0b5340b61252eed65a429fb7d6d3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>14.416</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.5312</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0xaf7225e255fd1aa5a0120e96f35eb9b1e1d0892e473941280163192b4505a376</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785560272</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>27.136</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xbf18e7eb65bd90202256497a7c99d689d7d5fc86b48dc91f52b24ca7605069cc</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.2488</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xc23f97461705ae01eb5a58d27789cd3f435cbaff7dc2c6e0adb3728285adb92a</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785560230</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>52.261307</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0xa064511d7251c47861886f5dbf258cfeb620bb8b4b87197300280c56d2ebabaa</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>28.47</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.6412</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x714b94ab9fe7c3181cb239c743b1739a5f8faf1aeba493c71aee3987557a383c</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785560230</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>44.397661</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xed36e22e1d3024216a1e4e5214f0f5936226bd5a45f76b8a400d0ba14f9ab0f8</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xc23f97461705ae01eb5a58d27789cd3f435cbaff7dc2c6e0adb3728285adb92a</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785560125</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xcc08d3e03e0339b39b9f64a338fddea3afc9476c06547d7f62a9968d96838b62</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10.99964</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.2512</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xc23f97461705ae01eb5a58d27789cd3f435cbaff7dc2c6e0adb3728285adb92a</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785560125</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>43.779662</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x6a736595238b7289278f1f7918ee308646944987aaeb83d3f113df2da8c9455a</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>13.75869</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.6113</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x27f03841ab4a6d97175c7cc224e59b6651eb8c019d998731a01f130598ddf62d</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785560125</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>22.509104</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x737fb23c3d510a642b5f5addc91c5708a08eaf1477079da007d961bdf4fb74c2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.6113</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x27f03841ab4a6d97175c7cc224e59b6651eb8c019d998731a01f130598ddf62d</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785560105</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>41.799591</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x2eb45dc0d093ece13bd0c130fcc9be2870292083f8f37f757261e1ee9d17945b</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19.03</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>FC Zurich</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>FC Zurich vs Servette FC</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>FC Zurich</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Servette FC</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x79ec2fb1ba4d59d205f3c3b373988cb21ec46407246c4cc128e20b477c2693e7</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19612584</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785559870</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>67.662222</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x7f030041576e23502086e1e1cbce4e6ee0c8e75d763accbde78926ee12594832</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>14.26</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.6425</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x714b94ab9fe7c3181cb239c743b1739a5f8faf1aeba493c71aee3987557a383c</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785557604</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>22.194553</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x4ffb7d05241408eb81c53e9611b8cc023047710b593080198d871fdbf6ccaaf8</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6.99977</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.2512</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xc23f97461705ae01eb5a58d27789cd3f435cbaff7dc2c6e0adb3728285adb92a</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785557604</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>27.859781</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x28e60f30e8d4504b8d0e310b416026227ff6a1c5ad02d56a2f6fdacfff30dc1e</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xc1BEa02928E7Dbb4b88c093f3EFC8FEcdC54334f</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>41.50757</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.3725</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>FC Thun vs BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>FC Thun</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x714b94ab9fe7c3181cb239c743b1739a5f8faf1aeba493c71aee3987557a383c</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19611697</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785551260</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785609000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>111.429718</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x889e4c26c8a497a646ccffadb2f3f1b24dbae2ec22c086b0017396209f4af21f</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>44.32</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.2475</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>FC Zurich vs Servette FC</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>FC Zurich</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Servette FC</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x61244a60fe501c549ef4ca5282d1ed97698790b1d8459a85a4e6a752833db822</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19612584</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785498956</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>179.070707</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x7e466b51d045dd066cda83c12f2c992ec4cbeefd40776cc17f43d42835cf1a8c</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>86.17</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.2425</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x6271898b21228abd7c9953532c10606a3a61b7474b6c0e00b81d6846b2a3a400</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785498935</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>355.340206</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0xd238f20fcde288ce4c57fbb8f7b33433a2d8034453a92004f2884ec326a64527</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.99999</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785472452</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>3.493432</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x1e132fb445f06c70fb459988df209de859a4064a819ad6bab3740c5a3eb17da8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.99999</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.5725</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>FC Basel vs FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>FC Lausanne-Sport</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19608292</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785472090</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785600000</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>3.493432</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>0x7417df48500a21fdf17e408e1817d476b873de30de27e939dc5f140ed6eb83a4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>1.5737</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Super League</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>FC Basel vs FC Lausanne-Sport</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>FC Basel</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>FC Lausanne-Sport</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>0xfc8ce8d533e549d1e6aca91b60884b272be0e67a9b5fa6a1ef4d23ebf5216175</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>L19608292</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>1785344488</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>1785600000</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>1.742902</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
